--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/BLINK/SPAgent_4B_px256k_pi3x_spatial_BLINK_exact_matching_result.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_px256k_pi3x_spatial/BLINK/SPAgent_4B_px256k_pi3x_spatial_BLINK_exact_matching_result.xlsx
@@ -1925,10 +1925,9 @@
 &lt;answer&gt;(A) left&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>The two images show the camera orbiting the green cup. In the first image (start), the cup is centered, and the checkered tablecloth is visible to the right and behind. In the second image (end), the cup is still centered, but the checkered tablecloth has shifted to the left and behind — indicating the camera has rotated counter-clockwise (left) around the cup.
-This corresponds to “left” movement (clockwise from the viewer’s perspective) — which, in the context of the problem, is defined as “left” (camera moving clockwise around the object).
-Thus, the correct answer is:
-&lt;answer&gt;(A) left&lt;/answer&gt;</t>
+    <t>The two images show a static scene with a green cup on a checkered tablecloth. The first image (left) shows the cup with its handle on the left side of the frame, and the second image (right) shows the cup with its handle now on the right side of the frame. This indicates that the camera has rotated around the object in a counter-clockwise direction, which corresponds to moving “right” (as defined in the problem: counter-clockwise = right).
+Thus, the camera is moving right.
+&lt;answer&gt;B&lt;/answer&gt;</t>
   </si>
   <si>
     <t>The two images show the same static scene from slightly different camera angles. The key observation is the relative positioning of the objects:
